--- a/3_Data_Dictionary/Global_Cybersecurity_Threats_2015-2024 (data_dictionary).xlsx
+++ b/3_Data_Dictionary/Global_Cybersecurity_Threats_2015-2024 (data_dictionary).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CD2476665F710D28/Desktop/Projects(sql)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd2476665f710d28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9279B6C-33B0-45A0-B01C-D05C21317CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7670398B-D216-43E4-BC81-6FCADD40E109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{195E3253-D444-4EB8-ABED-92688CB68F6B}"/>
   </bookViews>
